--- a/data_performance.xlsx
+++ b/data_performance.xlsx
@@ -43191,4618 +43191,6 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="393" xml:space="preserve">
-      <c r="A393">
-        <v>46200</v>
-      </c>
-      <c r="B393" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C393" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D393" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E393">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F393">
-        <v>1</v>
-      </c>
-      <c r="G393">
-        <v>1</v>
-      </c>
-      <c r="H393">
-        <v>1</v>
-      </c>
-      <c r="I393">
-        <v>1</v>
-      </c>
-      <c r="J393">
-        <v>1</v>
-      </c>
-      <c r="K393">
-        <v>0.96</v>
-      </c>
-      <c r="M393">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N393">
-        <v>0.9912</v>
-      </c>
-      <c r="O393">
-        <v>1</v>
-      </c>
-      <c r="P393">
-        <v>1</v>
-      </c>
-      <c r="Q393">
-        <v>0.9583</v>
-      </c>
-      <c r="R393">
-        <v>0.9</v>
-      </c>
-      <c r="S393">
-        <v>0.9038</v>
-      </c>
-      <c r="U393" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V393">
-        <v>1</v>
-      </c>
-      <c r="W393">
-        <v>1</v>
-      </c>
-      <c r="X393">
-        <v>1</v>
-      </c>
-      <c r="Y393">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z393">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA393">
-        <v>1</v>
-      </c>
-      <c r="AB393">
-        <v>1</v>
-      </c>
-      <c r="AC393">
-        <v>0.919</v>
-      </c>
-      <c r="AD393">
-        <v>1</v>
-      </c>
-      <c r="AE393">
-        <v>0.989</v>
-      </c>
-      <c r="AF393">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG393">
-        <v>1</v>
-      </c>
-      <c r="AH393" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI393" t="str">
-        <v>June</v>
-      </c>
-      <c r="AJ393" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="394" xml:space="preserve">
-      <c r="A394">
-        <v>46201</v>
-      </c>
-      <c r="B394" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C394" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D394" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E394">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F394">
-        <v>1</v>
-      </c>
-      <c r="G394">
-        <v>1</v>
-      </c>
-      <c r="H394">
-        <v>1</v>
-      </c>
-      <c r="I394">
-        <v>1</v>
-      </c>
-      <c r="J394">
-        <v>1</v>
-      </c>
-      <c r="K394">
-        <v>0.96</v>
-      </c>
-      <c r="M394">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N394">
-        <v>0.9912</v>
-      </c>
-      <c r="O394">
-        <v>1</v>
-      </c>
-      <c r="P394">
-        <v>1</v>
-      </c>
-      <c r="Q394">
-        <v>0.9583</v>
-      </c>
-      <c r="R394">
-        <v>0.9</v>
-      </c>
-      <c r="S394">
-        <v>0.9038</v>
-      </c>
-      <c r="U394" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V394">
-        <v>1</v>
-      </c>
-      <c r="W394">
-        <v>1</v>
-      </c>
-      <c r="X394">
-        <v>1</v>
-      </c>
-      <c r="Y394">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z394">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA394">
-        <v>1</v>
-      </c>
-      <c r="AB394">
-        <v>1</v>
-      </c>
-      <c r="AC394">
-        <v>0.919</v>
-      </c>
-      <c r="AD394">
-        <v>1</v>
-      </c>
-      <c r="AE394">
-        <v>0.989</v>
-      </c>
-      <c r="AF394">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG394">
-        <v>1</v>
-      </c>
-      <c r="AH394" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI394" t="str">
-        <v>June</v>
-      </c>
-      <c r="AJ394" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="395" xml:space="preserve">
-      <c r="A395">
-        <v>46202</v>
-      </c>
-      <c r="B395" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C395" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D395" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E395">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F395">
-        <v>1</v>
-      </c>
-      <c r="G395">
-        <v>1</v>
-      </c>
-      <c r="H395">
-        <v>1</v>
-      </c>
-      <c r="I395">
-        <v>1</v>
-      </c>
-      <c r="J395">
-        <v>1</v>
-      </c>
-      <c r="K395">
-        <v>0.96</v>
-      </c>
-      <c r="M395">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N395">
-        <v>0.9912</v>
-      </c>
-      <c r="O395">
-        <v>1</v>
-      </c>
-      <c r="P395">
-        <v>1</v>
-      </c>
-      <c r="Q395">
-        <v>0.9583</v>
-      </c>
-      <c r="R395">
-        <v>0.9</v>
-      </c>
-      <c r="S395">
-        <v>0.9038</v>
-      </c>
-      <c r="U395" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V395">
-        <v>1</v>
-      </c>
-      <c r="W395">
-        <v>1</v>
-      </c>
-      <c r="X395">
-        <v>1</v>
-      </c>
-      <c r="Y395">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z395">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA395">
-        <v>1</v>
-      </c>
-      <c r="AB395">
-        <v>1</v>
-      </c>
-      <c r="AC395">
-        <v>0.919</v>
-      </c>
-      <c r="AD395">
-        <v>1</v>
-      </c>
-      <c r="AE395">
-        <v>0.989</v>
-      </c>
-      <c r="AF395">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG395">
-        <v>1</v>
-      </c>
-      <c r="AH395" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI395" t="str">
-        <v>June</v>
-      </c>
-      <c r="AJ395" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="396" xml:space="preserve">
-      <c r="A396">
-        <v>46203</v>
-      </c>
-      <c r="B396" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C396" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D396" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E396">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F396">
-        <v>1</v>
-      </c>
-      <c r="G396">
-        <v>1</v>
-      </c>
-      <c r="H396">
-        <v>1</v>
-      </c>
-      <c r="I396">
-        <v>1</v>
-      </c>
-      <c r="J396">
-        <v>1</v>
-      </c>
-      <c r="K396">
-        <v>0.96</v>
-      </c>
-      <c r="M396">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N396">
-        <v>0.9912</v>
-      </c>
-      <c r="O396">
-        <v>1</v>
-      </c>
-      <c r="P396">
-        <v>1</v>
-      </c>
-      <c r="Q396">
-        <v>0.9583</v>
-      </c>
-      <c r="R396">
-        <v>0.9</v>
-      </c>
-      <c r="S396">
-        <v>0.9038</v>
-      </c>
-      <c r="U396" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V396">
-        <v>1</v>
-      </c>
-      <c r="W396">
-        <v>1</v>
-      </c>
-      <c r="X396">
-        <v>1</v>
-      </c>
-      <c r="Y396">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z396">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA396">
-        <v>1</v>
-      </c>
-      <c r="AB396">
-        <v>1</v>
-      </c>
-      <c r="AC396">
-        <v>0.919</v>
-      </c>
-      <c r="AD396">
-        <v>1</v>
-      </c>
-      <c r="AE396">
-        <v>0.989</v>
-      </c>
-      <c r="AF396">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG396">
-        <v>1</v>
-      </c>
-      <c r="AH396" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI396" t="str">
-        <v>June</v>
-      </c>
-      <c r="AJ396" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="397" xml:space="preserve">
-      <c r="A397">
-        <v>46204</v>
-      </c>
-      <c r="B397" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C397" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D397" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E397">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F397">
-        <v>1</v>
-      </c>
-      <c r="G397">
-        <v>1</v>
-      </c>
-      <c r="H397">
-        <v>1</v>
-      </c>
-      <c r="I397">
-        <v>1</v>
-      </c>
-      <c r="J397">
-        <v>1</v>
-      </c>
-      <c r="K397">
-        <v>0.96</v>
-      </c>
-      <c r="M397">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N397">
-        <v>0.9912</v>
-      </c>
-      <c r="O397">
-        <v>1</v>
-      </c>
-      <c r="P397">
-        <v>1</v>
-      </c>
-      <c r="Q397">
-        <v>0.9583</v>
-      </c>
-      <c r="R397">
-        <v>0.9</v>
-      </c>
-      <c r="S397">
-        <v>0.9038</v>
-      </c>
-      <c r="U397" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V397">
-        <v>1</v>
-      </c>
-      <c r="W397">
-        <v>1</v>
-      </c>
-      <c r="X397">
-        <v>1</v>
-      </c>
-      <c r="Y397">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z397">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA397">
-        <v>1</v>
-      </c>
-      <c r="AB397">
-        <v>1</v>
-      </c>
-      <c r="AC397">
-        <v>0.919</v>
-      </c>
-      <c r="AD397">
-        <v>1</v>
-      </c>
-      <c r="AE397">
-        <v>0.994</v>
-      </c>
-      <c r="AF397">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG397">
-        <v>1</v>
-      </c>
-      <c r="AH397" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI397" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ397" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="398" xml:space="preserve">
-      <c r="A398">
-        <v>46205</v>
-      </c>
-      <c r="B398" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C398" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D398" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E398">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F398">
-        <v>1</v>
-      </c>
-      <c r="G398">
-        <v>1</v>
-      </c>
-      <c r="H398">
-        <v>1</v>
-      </c>
-      <c r="I398">
-        <v>1</v>
-      </c>
-      <c r="J398">
-        <v>1</v>
-      </c>
-      <c r="K398">
-        <v>0.96</v>
-      </c>
-      <c r="M398">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N398">
-        <v>0.9912</v>
-      </c>
-      <c r="O398">
-        <v>1</v>
-      </c>
-      <c r="P398">
-        <v>1</v>
-      </c>
-      <c r="Q398">
-        <v>0.9583</v>
-      </c>
-      <c r="R398">
-        <v>0.9</v>
-      </c>
-      <c r="S398">
-        <v>0.9038</v>
-      </c>
-      <c r="U398" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V398">
-        <v>1</v>
-      </c>
-      <c r="W398">
-        <v>1</v>
-      </c>
-      <c r="X398">
-        <v>1</v>
-      </c>
-      <c r="Y398">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z398">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA398">
-        <v>1</v>
-      </c>
-      <c r="AB398">
-        <v>1</v>
-      </c>
-      <c r="AC398">
-        <v>0.919</v>
-      </c>
-      <c r="AD398">
-        <v>1</v>
-      </c>
-      <c r="AE398">
-        <v>0.994</v>
-      </c>
-      <c r="AF398">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG398">
-        <v>1</v>
-      </c>
-      <c r="AH398" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI398" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ398" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="399" xml:space="preserve">
-      <c r="A399">
-        <v>46206</v>
-      </c>
-      <c r="B399" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C399" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D399" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E399">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F399">
-        <v>1</v>
-      </c>
-      <c r="G399">
-        <v>1</v>
-      </c>
-      <c r="H399">
-        <v>1</v>
-      </c>
-      <c r="I399">
-        <v>1</v>
-      </c>
-      <c r="J399">
-        <v>1</v>
-      </c>
-      <c r="K399">
-        <v>0.96</v>
-      </c>
-      <c r="M399">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N399">
-        <v>0.9912</v>
-      </c>
-      <c r="O399">
-        <v>1</v>
-      </c>
-      <c r="P399">
-        <v>1</v>
-      </c>
-      <c r="Q399">
-        <v>0.9583</v>
-      </c>
-      <c r="R399">
-        <v>0.9</v>
-      </c>
-      <c r="S399">
-        <v>0.9038</v>
-      </c>
-      <c r="U399" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V399">
-        <v>1</v>
-      </c>
-      <c r="W399">
-        <v>1</v>
-      </c>
-      <c r="X399">
-        <v>1</v>
-      </c>
-      <c r="Y399">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z399">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA399">
-        <v>1</v>
-      </c>
-      <c r="AB399">
-        <v>1</v>
-      </c>
-      <c r="AC399">
-        <v>0.919</v>
-      </c>
-      <c r="AD399">
-        <v>1</v>
-      </c>
-      <c r="AE399">
-        <v>0.994</v>
-      </c>
-      <c r="AF399">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG399">
-        <v>1</v>
-      </c>
-      <c r="AH399" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI399" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ399" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="400" xml:space="preserve">
-      <c r="A400">
-        <v>46207</v>
-      </c>
-      <c r="B400" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C400" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D400" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E400">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F400">
-        <v>1</v>
-      </c>
-      <c r="G400">
-        <v>1</v>
-      </c>
-      <c r="H400">
-        <v>1</v>
-      </c>
-      <c r="I400">
-        <v>1</v>
-      </c>
-      <c r="J400">
-        <v>1</v>
-      </c>
-      <c r="K400">
-        <v>0.96</v>
-      </c>
-      <c r="M400">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N400">
-        <v>0.9912</v>
-      </c>
-      <c r="O400">
-        <v>1</v>
-      </c>
-      <c r="P400">
-        <v>1</v>
-      </c>
-      <c r="Q400">
-        <v>0.9583</v>
-      </c>
-      <c r="R400">
-        <v>0.9</v>
-      </c>
-      <c r="S400">
-        <v>0.9038</v>
-      </c>
-      <c r="U400" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V400">
-        <v>1</v>
-      </c>
-      <c r="W400">
-        <v>1</v>
-      </c>
-      <c r="X400">
-        <v>1</v>
-      </c>
-      <c r="Y400">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z400">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA400">
-        <v>1</v>
-      </c>
-      <c r="AB400">
-        <v>1</v>
-      </c>
-      <c r="AC400">
-        <v>0.919</v>
-      </c>
-      <c r="AD400">
-        <v>1</v>
-      </c>
-      <c r="AE400">
-        <v>0.994</v>
-      </c>
-      <c r="AF400">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG400">
-        <v>1</v>
-      </c>
-      <c r="AH400" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI400" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ400" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="401" xml:space="preserve">
-      <c r="A401">
-        <v>46208</v>
-      </c>
-      <c r="B401" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C401" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D401" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E401">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F401">
-        <v>1</v>
-      </c>
-      <c r="G401">
-        <v>1</v>
-      </c>
-      <c r="H401">
-        <v>1</v>
-      </c>
-      <c r="I401">
-        <v>1</v>
-      </c>
-      <c r="J401">
-        <v>1</v>
-      </c>
-      <c r="K401">
-        <v>0.96</v>
-      </c>
-      <c r="M401">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N401">
-        <v>0.9912</v>
-      </c>
-      <c r="O401">
-        <v>1</v>
-      </c>
-      <c r="P401">
-        <v>1</v>
-      </c>
-      <c r="Q401">
-        <v>0.9583</v>
-      </c>
-      <c r="R401">
-        <v>0.9</v>
-      </c>
-      <c r="S401">
-        <v>0.9038</v>
-      </c>
-      <c r="U401" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V401">
-        <v>1</v>
-      </c>
-      <c r="W401">
-        <v>1</v>
-      </c>
-      <c r="X401">
-        <v>1</v>
-      </c>
-      <c r="Y401">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z401">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA401">
-        <v>1</v>
-      </c>
-      <c r="AB401">
-        <v>1</v>
-      </c>
-      <c r="AC401">
-        <v>0.919</v>
-      </c>
-      <c r="AD401">
-        <v>1</v>
-      </c>
-      <c r="AE401">
-        <v>0.994</v>
-      </c>
-      <c r="AF401">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG401">
-        <v>1</v>
-      </c>
-      <c r="AH401" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI401" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ401" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="402" xml:space="preserve">
-      <c r="A402">
-        <v>46209</v>
-      </c>
-      <c r="B402" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C402" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D402" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E402">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F402">
-        <v>1</v>
-      </c>
-      <c r="G402">
-        <v>1</v>
-      </c>
-      <c r="H402">
-        <v>1</v>
-      </c>
-      <c r="I402">
-        <v>1</v>
-      </c>
-      <c r="J402">
-        <v>1</v>
-      </c>
-      <c r="K402">
-        <v>0.96</v>
-      </c>
-      <c r="M402">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N402">
-        <v>0.9912</v>
-      </c>
-      <c r="O402">
-        <v>1</v>
-      </c>
-      <c r="P402">
-        <v>1</v>
-      </c>
-      <c r="Q402">
-        <v>0.9583</v>
-      </c>
-      <c r="R402">
-        <v>0.9</v>
-      </c>
-      <c r="S402">
-        <v>0.9038</v>
-      </c>
-      <c r="U402" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V402">
-        <v>1</v>
-      </c>
-      <c r="W402">
-        <v>1</v>
-      </c>
-      <c r="X402">
-        <v>1</v>
-      </c>
-      <c r="Y402">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z402">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA402">
-        <v>1</v>
-      </c>
-      <c r="AB402">
-        <v>1</v>
-      </c>
-      <c r="AC402">
-        <v>0.919</v>
-      </c>
-      <c r="AD402">
-        <v>1</v>
-      </c>
-      <c r="AE402">
-        <v>0.994</v>
-      </c>
-      <c r="AF402">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG402">
-        <v>1</v>
-      </c>
-      <c r="AH402" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI402" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ402" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="403" xml:space="preserve">
-      <c r="A403">
-        <v>46210</v>
-      </c>
-      <c r="B403" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C403" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D403" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E403">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F403">
-        <v>1</v>
-      </c>
-      <c r="G403">
-        <v>1</v>
-      </c>
-      <c r="H403">
-        <v>1</v>
-      </c>
-      <c r="I403">
-        <v>1</v>
-      </c>
-      <c r="J403">
-        <v>1</v>
-      </c>
-      <c r="K403">
-        <v>0.96</v>
-      </c>
-      <c r="M403">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N403">
-        <v>0.9912</v>
-      </c>
-      <c r="O403">
-        <v>1</v>
-      </c>
-      <c r="P403">
-        <v>1</v>
-      </c>
-      <c r="Q403">
-        <v>0.9583</v>
-      </c>
-      <c r="R403">
-        <v>0.9</v>
-      </c>
-      <c r="S403">
-        <v>0.9038</v>
-      </c>
-      <c r="U403" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V403">
-        <v>1</v>
-      </c>
-      <c r="W403">
-        <v>1</v>
-      </c>
-      <c r="X403">
-        <v>1</v>
-      </c>
-      <c r="Y403">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z403">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA403">
-        <v>1</v>
-      </c>
-      <c r="AB403">
-        <v>1</v>
-      </c>
-      <c r="AC403">
-        <v>0.919</v>
-      </c>
-      <c r="AD403">
-        <v>1</v>
-      </c>
-      <c r="AE403">
-        <v>0.994</v>
-      </c>
-      <c r="AF403">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG403">
-        <v>1</v>
-      </c>
-      <c r="AH403" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI403" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ403" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="404" xml:space="preserve">
-      <c r="A404">
-        <v>46211</v>
-      </c>
-      <c r="B404" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C404" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D404" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E404">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F404">
-        <v>1</v>
-      </c>
-      <c r="G404">
-        <v>1</v>
-      </c>
-      <c r="H404">
-        <v>1</v>
-      </c>
-      <c r="I404">
-        <v>1</v>
-      </c>
-      <c r="J404">
-        <v>1</v>
-      </c>
-      <c r="K404">
-        <v>0.96</v>
-      </c>
-      <c r="M404">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N404">
-        <v>0.9912</v>
-      </c>
-      <c r="O404">
-        <v>1</v>
-      </c>
-      <c r="P404">
-        <v>1</v>
-      </c>
-      <c r="Q404">
-        <v>0.9583</v>
-      </c>
-      <c r="R404">
-        <v>0.9</v>
-      </c>
-      <c r="S404">
-        <v>0.9038</v>
-      </c>
-      <c r="U404" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V404">
-        <v>1</v>
-      </c>
-      <c r="W404">
-        <v>1</v>
-      </c>
-      <c r="X404">
-        <v>1</v>
-      </c>
-      <c r="Y404">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z404">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA404">
-        <v>1</v>
-      </c>
-      <c r="AB404">
-        <v>1</v>
-      </c>
-      <c r="AC404">
-        <v>0.919</v>
-      </c>
-      <c r="AD404">
-        <v>1</v>
-      </c>
-      <c r="AE404">
-        <v>0.994</v>
-      </c>
-      <c r="AF404">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG404">
-        <v>1</v>
-      </c>
-      <c r="AH404" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI404" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ404" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="405" xml:space="preserve">
-      <c r="A405">
-        <v>46212</v>
-      </c>
-      <c r="B405" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C405" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D405" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E405">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F405">
-        <v>1</v>
-      </c>
-      <c r="G405">
-        <v>1</v>
-      </c>
-      <c r="H405">
-        <v>1</v>
-      </c>
-      <c r="I405">
-        <v>1</v>
-      </c>
-      <c r="J405">
-        <v>1</v>
-      </c>
-      <c r="K405">
-        <v>0.96</v>
-      </c>
-      <c r="M405">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N405">
-        <v>0.9912</v>
-      </c>
-      <c r="O405">
-        <v>1</v>
-      </c>
-      <c r="P405">
-        <v>1</v>
-      </c>
-      <c r="Q405">
-        <v>0.9583</v>
-      </c>
-      <c r="R405">
-        <v>0.9</v>
-      </c>
-      <c r="S405">
-        <v>0.9038</v>
-      </c>
-      <c r="U405" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V405">
-        <v>1</v>
-      </c>
-      <c r="W405">
-        <v>1</v>
-      </c>
-      <c r="X405">
-        <v>1</v>
-      </c>
-      <c r="Y405">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z405">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA405">
-        <v>1</v>
-      </c>
-      <c r="AB405">
-        <v>1</v>
-      </c>
-      <c r="AC405">
-        <v>0.919</v>
-      </c>
-      <c r="AD405">
-        <v>1</v>
-      </c>
-      <c r="AE405">
-        <v>0.994</v>
-      </c>
-      <c r="AF405">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG405">
-        <v>1</v>
-      </c>
-      <c r="AH405" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI405" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ405" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="406" xml:space="preserve">
-      <c r="A406">
-        <v>46213</v>
-      </c>
-      <c r="B406" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C406" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D406" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E406">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F406">
-        <v>1</v>
-      </c>
-      <c r="G406">
-        <v>1</v>
-      </c>
-      <c r="H406">
-        <v>1</v>
-      </c>
-      <c r="I406">
-        <v>1</v>
-      </c>
-      <c r="J406">
-        <v>1</v>
-      </c>
-      <c r="K406">
-        <v>0.96</v>
-      </c>
-      <c r="M406">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N406">
-        <v>0.9912</v>
-      </c>
-      <c r="O406">
-        <v>1</v>
-      </c>
-      <c r="P406">
-        <v>1</v>
-      </c>
-      <c r="Q406">
-        <v>0.9583</v>
-      </c>
-      <c r="R406">
-        <v>0.9</v>
-      </c>
-      <c r="S406">
-        <v>0.9038</v>
-      </c>
-      <c r="U406" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V406">
-        <v>1</v>
-      </c>
-      <c r="W406">
-        <v>1</v>
-      </c>
-      <c r="X406">
-        <v>1</v>
-      </c>
-      <c r="Y406">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z406">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA406">
-        <v>1</v>
-      </c>
-      <c r="AB406">
-        <v>1</v>
-      </c>
-      <c r="AC406">
-        <v>0.919</v>
-      </c>
-      <c r="AD406">
-        <v>1</v>
-      </c>
-      <c r="AE406">
-        <v>0.994</v>
-      </c>
-      <c r="AF406">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG406">
-        <v>1</v>
-      </c>
-      <c r="AH406" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI406" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ406" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="407" xml:space="preserve">
-      <c r="A407">
-        <v>46214</v>
-      </c>
-      <c r="B407" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C407" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D407" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E407">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F407">
-        <v>1</v>
-      </c>
-      <c r="G407">
-        <v>1</v>
-      </c>
-      <c r="H407">
-        <v>1</v>
-      </c>
-      <c r="I407">
-        <v>1</v>
-      </c>
-      <c r="J407">
-        <v>1</v>
-      </c>
-      <c r="K407">
-        <v>0.96</v>
-      </c>
-      <c r="M407">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N407">
-        <v>0.9912</v>
-      </c>
-      <c r="O407">
-        <v>1</v>
-      </c>
-      <c r="P407">
-        <v>1</v>
-      </c>
-      <c r="Q407">
-        <v>0.9583</v>
-      </c>
-      <c r="R407">
-        <v>0.9</v>
-      </c>
-      <c r="S407">
-        <v>0.9038</v>
-      </c>
-      <c r="U407" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V407">
-        <v>1</v>
-      </c>
-      <c r="W407">
-        <v>1</v>
-      </c>
-      <c r="X407">
-        <v>1</v>
-      </c>
-      <c r="Y407">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z407">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA407">
-        <v>1</v>
-      </c>
-      <c r="AB407">
-        <v>1</v>
-      </c>
-      <c r="AC407">
-        <v>0.919</v>
-      </c>
-      <c r="AD407">
-        <v>1</v>
-      </c>
-      <c r="AE407">
-        <v>0.994</v>
-      </c>
-      <c r="AF407">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG407">
-        <v>1</v>
-      </c>
-      <c r="AH407" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI407" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ407" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="408" xml:space="preserve">
-      <c r="A408">
-        <v>46215</v>
-      </c>
-      <c r="B408" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C408" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D408" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E408">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F408">
-        <v>1</v>
-      </c>
-      <c r="G408">
-        <v>1</v>
-      </c>
-      <c r="H408">
-        <v>1</v>
-      </c>
-      <c r="I408">
-        <v>1</v>
-      </c>
-      <c r="J408">
-        <v>1</v>
-      </c>
-      <c r="K408">
-        <v>0.96</v>
-      </c>
-      <c r="M408">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N408">
-        <v>0.9912</v>
-      </c>
-      <c r="O408">
-        <v>1</v>
-      </c>
-      <c r="P408">
-        <v>1</v>
-      </c>
-      <c r="Q408">
-        <v>0.9583</v>
-      </c>
-      <c r="R408">
-        <v>0.9</v>
-      </c>
-      <c r="S408">
-        <v>0.9038</v>
-      </c>
-      <c r="U408" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V408">
-        <v>1</v>
-      </c>
-      <c r="W408">
-        <v>1</v>
-      </c>
-      <c r="X408">
-        <v>1</v>
-      </c>
-      <c r="Y408">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z408">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA408">
-        <v>1</v>
-      </c>
-      <c r="AB408">
-        <v>1</v>
-      </c>
-      <c r="AC408">
-        <v>0.919</v>
-      </c>
-      <c r="AD408">
-        <v>1</v>
-      </c>
-      <c r="AE408">
-        <v>0.994</v>
-      </c>
-      <c r="AF408">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG408">
-        <v>1</v>
-      </c>
-      <c r="AH408" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI408" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ408" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="409" xml:space="preserve">
-      <c r="A409">
-        <v>46216</v>
-      </c>
-      <c r="B409" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C409" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D409" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E409">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F409">
-        <v>1</v>
-      </c>
-      <c r="G409">
-        <v>1</v>
-      </c>
-      <c r="H409">
-        <v>1</v>
-      </c>
-      <c r="I409">
-        <v>1</v>
-      </c>
-      <c r="J409">
-        <v>1</v>
-      </c>
-      <c r="K409">
-        <v>0.96</v>
-      </c>
-      <c r="M409">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N409">
-        <v>0.9912</v>
-      </c>
-      <c r="O409">
-        <v>1</v>
-      </c>
-      <c r="P409">
-        <v>1</v>
-      </c>
-      <c r="Q409">
-        <v>0.9583</v>
-      </c>
-      <c r="R409">
-        <v>0.9</v>
-      </c>
-      <c r="S409">
-        <v>0.9038</v>
-      </c>
-      <c r="U409" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V409">
-        <v>1</v>
-      </c>
-      <c r="W409">
-        <v>1</v>
-      </c>
-      <c r="X409">
-        <v>1</v>
-      </c>
-      <c r="Y409">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z409">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA409">
-        <v>1</v>
-      </c>
-      <c r="AB409">
-        <v>1</v>
-      </c>
-      <c r="AC409">
-        <v>0.919</v>
-      </c>
-      <c r="AD409">
-        <v>1</v>
-      </c>
-      <c r="AE409">
-        <v>0.994</v>
-      </c>
-      <c r="AF409">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG409">
-        <v>1</v>
-      </c>
-      <c r="AH409" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI409" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ409" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="410" xml:space="preserve">
-      <c r="A410">
-        <v>46217</v>
-      </c>
-      <c r="B410" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C410" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D410" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E410">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F410">
-        <v>1</v>
-      </c>
-      <c r="G410">
-        <v>1</v>
-      </c>
-      <c r="H410">
-        <v>1</v>
-      </c>
-      <c r="I410">
-        <v>1</v>
-      </c>
-      <c r="J410">
-        <v>1</v>
-      </c>
-      <c r="K410">
-        <v>0.96</v>
-      </c>
-      <c r="M410">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N410">
-        <v>0.9912</v>
-      </c>
-      <c r="O410">
-        <v>1</v>
-      </c>
-      <c r="P410">
-        <v>1</v>
-      </c>
-      <c r="Q410">
-        <v>0.9583</v>
-      </c>
-      <c r="R410">
-        <v>0.9</v>
-      </c>
-      <c r="S410">
-        <v>0.9038</v>
-      </c>
-      <c r="U410" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V410">
-        <v>1</v>
-      </c>
-      <c r="W410">
-        <v>1</v>
-      </c>
-      <c r="X410">
-        <v>1</v>
-      </c>
-      <c r="Y410">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z410">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA410">
-        <v>1</v>
-      </c>
-      <c r="AB410">
-        <v>1</v>
-      </c>
-      <c r="AC410">
-        <v>0.919</v>
-      </c>
-      <c r="AD410">
-        <v>1</v>
-      </c>
-      <c r="AE410">
-        <v>0.994</v>
-      </c>
-      <c r="AF410">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG410">
-        <v>1</v>
-      </c>
-      <c r="AH410" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI410" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ410" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="411" xml:space="preserve">
-      <c r="A411">
-        <v>46218</v>
-      </c>
-      <c r="B411" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C411" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D411" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E411">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F411">
-        <v>1</v>
-      </c>
-      <c r="G411">
-        <v>1</v>
-      </c>
-      <c r="H411">
-        <v>1</v>
-      </c>
-      <c r="I411">
-        <v>1</v>
-      </c>
-      <c r="J411">
-        <v>1</v>
-      </c>
-      <c r="K411">
-        <v>0.96</v>
-      </c>
-      <c r="M411">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N411">
-        <v>0.9912</v>
-      </c>
-      <c r="O411">
-        <v>1</v>
-      </c>
-      <c r="P411">
-        <v>1</v>
-      </c>
-      <c r="Q411">
-        <v>0.9583</v>
-      </c>
-      <c r="R411">
-        <v>0.9</v>
-      </c>
-      <c r="S411">
-        <v>0.9038</v>
-      </c>
-      <c r="U411" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V411">
-        <v>1</v>
-      </c>
-      <c r="W411">
-        <v>1</v>
-      </c>
-      <c r="X411">
-        <v>1</v>
-      </c>
-      <c r="Y411">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z411">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA411">
-        <v>1</v>
-      </c>
-      <c r="AB411">
-        <v>1</v>
-      </c>
-      <c r="AC411">
-        <v>0.919</v>
-      </c>
-      <c r="AD411">
-        <v>1</v>
-      </c>
-      <c r="AE411">
-        <v>0.994</v>
-      </c>
-      <c r="AF411">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG411">
-        <v>1</v>
-      </c>
-      <c r="AH411" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI411" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ411" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="412" xml:space="preserve">
-      <c r="A412">
-        <v>46219</v>
-      </c>
-      <c r="B412" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C412" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D412" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E412">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F412">
-        <v>1</v>
-      </c>
-      <c r="G412">
-        <v>1</v>
-      </c>
-      <c r="H412">
-        <v>1</v>
-      </c>
-      <c r="I412">
-        <v>1</v>
-      </c>
-      <c r="J412">
-        <v>1</v>
-      </c>
-      <c r="K412">
-        <v>0.96</v>
-      </c>
-      <c r="M412">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N412">
-        <v>0.9912</v>
-      </c>
-      <c r="O412">
-        <v>1</v>
-      </c>
-      <c r="P412">
-        <v>1</v>
-      </c>
-      <c r="Q412">
-        <v>0.9583</v>
-      </c>
-      <c r="R412">
-        <v>0.9</v>
-      </c>
-      <c r="S412">
-        <v>0.9038</v>
-      </c>
-      <c r="U412" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V412">
-        <v>1</v>
-      </c>
-      <c r="W412">
-        <v>1</v>
-      </c>
-      <c r="X412">
-        <v>1</v>
-      </c>
-      <c r="Y412">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z412">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA412">
-        <v>1</v>
-      </c>
-      <c r="AB412">
-        <v>1</v>
-      </c>
-      <c r="AC412">
-        <v>0.919</v>
-      </c>
-      <c r="AD412">
-        <v>1</v>
-      </c>
-      <c r="AE412">
-        <v>0.994</v>
-      </c>
-      <c r="AF412">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG412">
-        <v>1</v>
-      </c>
-      <c r="AH412" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI412" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ412" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="413" xml:space="preserve">
-      <c r="A413">
-        <v>46220</v>
-      </c>
-      <c r="B413" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C413" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D413" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E413">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F413">
-        <v>1</v>
-      </c>
-      <c r="G413">
-        <v>1</v>
-      </c>
-      <c r="H413">
-        <v>1</v>
-      </c>
-      <c r="I413">
-        <v>1</v>
-      </c>
-      <c r="J413">
-        <v>1</v>
-      </c>
-      <c r="K413">
-        <v>0.96</v>
-      </c>
-      <c r="M413">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N413">
-        <v>0.9912</v>
-      </c>
-      <c r="O413">
-        <v>1</v>
-      </c>
-      <c r="P413">
-        <v>1</v>
-      </c>
-      <c r="Q413">
-        <v>0.9583</v>
-      </c>
-      <c r="R413">
-        <v>0.9</v>
-      </c>
-      <c r="S413">
-        <v>0.9038</v>
-      </c>
-      <c r="U413" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V413">
-        <v>1</v>
-      </c>
-      <c r="W413">
-        <v>1</v>
-      </c>
-      <c r="X413">
-        <v>1</v>
-      </c>
-      <c r="Y413">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z413">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA413">
-        <v>1</v>
-      </c>
-      <c r="AB413">
-        <v>1</v>
-      </c>
-      <c r="AC413">
-        <v>0.919</v>
-      </c>
-      <c r="AD413">
-        <v>1</v>
-      </c>
-      <c r="AE413">
-        <v>0.994</v>
-      </c>
-      <c r="AF413">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG413">
-        <v>1</v>
-      </c>
-      <c r="AH413" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI413" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ413" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="414" xml:space="preserve">
-      <c r="A414">
-        <v>46221</v>
-      </c>
-      <c r="B414" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C414" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D414" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E414">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F414">
-        <v>1</v>
-      </c>
-      <c r="G414">
-        <v>1</v>
-      </c>
-      <c r="H414">
-        <v>1</v>
-      </c>
-      <c r="I414">
-        <v>1</v>
-      </c>
-      <c r="J414">
-        <v>1</v>
-      </c>
-      <c r="K414">
-        <v>0.96</v>
-      </c>
-      <c r="M414">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N414">
-        <v>0.9912</v>
-      </c>
-      <c r="O414">
-        <v>1</v>
-      </c>
-      <c r="P414">
-        <v>1</v>
-      </c>
-      <c r="Q414">
-        <v>0.9583</v>
-      </c>
-      <c r="R414">
-        <v>0.9</v>
-      </c>
-      <c r="S414">
-        <v>0.9038</v>
-      </c>
-      <c r="U414" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V414">
-        <v>1</v>
-      </c>
-      <c r="W414">
-        <v>1</v>
-      </c>
-      <c r="X414">
-        <v>1</v>
-      </c>
-      <c r="Y414">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z414">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA414">
-        <v>1</v>
-      </c>
-      <c r="AB414">
-        <v>1</v>
-      </c>
-      <c r="AC414">
-        <v>0.919</v>
-      </c>
-      <c r="AD414">
-        <v>1</v>
-      </c>
-      <c r="AE414">
-        <v>0.994</v>
-      </c>
-      <c r="AF414">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG414">
-        <v>1</v>
-      </c>
-      <c r="AH414" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI414" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ414" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="415" xml:space="preserve">
-      <c r="A415">
-        <v>46222</v>
-      </c>
-      <c r="B415" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C415" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D415" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E415">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F415">
-        <v>1</v>
-      </c>
-      <c r="G415">
-        <v>1</v>
-      </c>
-      <c r="H415">
-        <v>1</v>
-      </c>
-      <c r="I415">
-        <v>1</v>
-      </c>
-      <c r="J415">
-        <v>1</v>
-      </c>
-      <c r="K415">
-        <v>0.96</v>
-      </c>
-      <c r="M415">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N415">
-        <v>0.9912</v>
-      </c>
-      <c r="O415">
-        <v>1</v>
-      </c>
-      <c r="P415">
-        <v>1</v>
-      </c>
-      <c r="Q415">
-        <v>0.9583</v>
-      </c>
-      <c r="R415">
-        <v>0.9</v>
-      </c>
-      <c r="S415">
-        <v>0.9038</v>
-      </c>
-      <c r="U415" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V415">
-        <v>1</v>
-      </c>
-      <c r="W415">
-        <v>1</v>
-      </c>
-      <c r="X415">
-        <v>1</v>
-      </c>
-      <c r="Y415">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z415">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA415">
-        <v>1</v>
-      </c>
-      <c r="AB415">
-        <v>1</v>
-      </c>
-      <c r="AC415">
-        <v>0.919</v>
-      </c>
-      <c r="AD415">
-        <v>1</v>
-      </c>
-      <c r="AE415">
-        <v>0.994</v>
-      </c>
-      <c r="AF415">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG415">
-        <v>1</v>
-      </c>
-      <c r="AH415" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI415" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ415" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="416" xml:space="preserve">
-      <c r="A416">
-        <v>46223</v>
-      </c>
-      <c r="B416" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C416" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D416" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E416">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F416">
-        <v>1</v>
-      </c>
-      <c r="G416">
-        <v>1</v>
-      </c>
-      <c r="H416">
-        <v>1</v>
-      </c>
-      <c r="I416">
-        <v>1</v>
-      </c>
-      <c r="J416">
-        <v>1</v>
-      </c>
-      <c r="K416">
-        <v>0.96</v>
-      </c>
-      <c r="M416">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N416">
-        <v>0.9912</v>
-      </c>
-      <c r="O416">
-        <v>1</v>
-      </c>
-      <c r="P416">
-        <v>1</v>
-      </c>
-      <c r="Q416">
-        <v>0.9583</v>
-      </c>
-      <c r="R416">
-        <v>0.9</v>
-      </c>
-      <c r="S416">
-        <v>0.9038</v>
-      </c>
-      <c r="U416" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V416">
-        <v>1</v>
-      </c>
-      <c r="W416">
-        <v>1</v>
-      </c>
-      <c r="X416">
-        <v>1</v>
-      </c>
-      <c r="Y416">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z416">
-        <v>0.941999999999999</v>
-      </c>
-      <c r="AA416">
-        <v>1</v>
-      </c>
-      <c r="AB416">
-        <v>1</v>
-      </c>
-      <c r="AC416">
-        <v>0.919</v>
-      </c>
-      <c r="AD416">
-        <v>1</v>
-      </c>
-      <c r="AE416">
-        <v>0.994</v>
-      </c>
-      <c r="AF416">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG416">
-        <v>1</v>
-      </c>
-      <c r="AH416" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI416" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ416" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="417" xml:space="preserve">
-      <c r="A417">
-        <v>46224</v>
-      </c>
-      <c r="B417" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C417" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D417" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E417">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F417">
-        <v>1</v>
-      </c>
-      <c r="G417">
-        <v>1</v>
-      </c>
-      <c r="H417">
-        <v>1</v>
-      </c>
-      <c r="I417">
-        <v>1</v>
-      </c>
-      <c r="J417">
-        <v>1</v>
-      </c>
-      <c r="K417">
-        <v>0.96</v>
-      </c>
-      <c r="M417">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N417">
-        <v>0.9912</v>
-      </c>
-      <c r="O417">
-        <v>1</v>
-      </c>
-      <c r="P417">
-        <v>1</v>
-      </c>
-      <c r="Q417">
-        <v>0.9583</v>
-      </c>
-      <c r="R417">
-        <v>0.9</v>
-      </c>
-      <c r="S417">
-        <v>0.9038</v>
-      </c>
-      <c r="U417" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V417">
-        <v>1</v>
-      </c>
-      <c r="W417">
-        <v>1</v>
-      </c>
-      <c r="X417">
-        <v>1</v>
-      </c>
-      <c r="Y417">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z417">
-        <v>0.946</v>
-      </c>
-      <c r="AA417">
-        <v>1</v>
-      </c>
-      <c r="AB417">
-        <v>1</v>
-      </c>
-      <c r="AC417">
-        <v>0.919</v>
-      </c>
-      <c r="AD417">
-        <v>1</v>
-      </c>
-      <c r="AE417">
-        <v>0.994</v>
-      </c>
-      <c r="AF417">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG417">
-        <v>1</v>
-      </c>
-      <c r="AH417" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI417" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ417" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="418" xml:space="preserve">
-      <c r="A418">
-        <v>46225</v>
-      </c>
-      <c r="B418" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C418" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D418" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E418">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F418">
-        <v>1</v>
-      </c>
-      <c r="G418">
-        <v>1</v>
-      </c>
-      <c r="H418">
-        <v>1</v>
-      </c>
-      <c r="I418">
-        <v>1</v>
-      </c>
-      <c r="J418">
-        <v>1</v>
-      </c>
-      <c r="K418">
-        <v>0.96</v>
-      </c>
-      <c r="M418">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N418">
-        <v>0.9912</v>
-      </c>
-      <c r="O418">
-        <v>1</v>
-      </c>
-      <c r="P418">
-        <v>1</v>
-      </c>
-      <c r="Q418">
-        <v>0.9583</v>
-      </c>
-      <c r="R418">
-        <v>0.9</v>
-      </c>
-      <c r="S418">
-        <v>0.9038</v>
-      </c>
-      <c r="U418" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V418">
-        <v>1</v>
-      </c>
-      <c r="W418">
-        <v>1</v>
-      </c>
-      <c r="X418">
-        <v>1</v>
-      </c>
-      <c r="Y418">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z418">
-        <v>0.946</v>
-      </c>
-      <c r="AA418">
-        <v>1</v>
-      </c>
-      <c r="AB418">
-        <v>1</v>
-      </c>
-      <c r="AC418">
-        <v>0.919</v>
-      </c>
-      <c r="AD418">
-        <v>1</v>
-      </c>
-      <c r="AE418">
-        <v>0.994</v>
-      </c>
-      <c r="AF418">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG418">
-        <v>1</v>
-      </c>
-      <c r="AH418" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI418" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ418" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="419" xml:space="preserve">
-      <c r="A419">
-        <v>46226</v>
-      </c>
-      <c r="B419" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C419" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D419" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E419">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F419">
-        <v>1</v>
-      </c>
-      <c r="G419">
-        <v>1</v>
-      </c>
-      <c r="H419">
-        <v>1</v>
-      </c>
-      <c r="I419">
-        <v>1</v>
-      </c>
-      <c r="J419">
-        <v>1</v>
-      </c>
-      <c r="K419">
-        <v>0.96</v>
-      </c>
-      <c r="M419">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N419">
-        <v>0.9912</v>
-      </c>
-      <c r="O419">
-        <v>1</v>
-      </c>
-      <c r="P419">
-        <v>1</v>
-      </c>
-      <c r="Q419">
-        <v>0.9583</v>
-      </c>
-      <c r="R419">
-        <v>0.9</v>
-      </c>
-      <c r="S419">
-        <v>0.9038</v>
-      </c>
-      <c r="U419" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V419">
-        <v>1</v>
-      </c>
-      <c r="W419">
-        <v>1</v>
-      </c>
-      <c r="X419">
-        <v>1</v>
-      </c>
-      <c r="Y419">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z419">
-        <v>0.946</v>
-      </c>
-      <c r="AA419">
-        <v>1</v>
-      </c>
-      <c r="AB419">
-        <v>1</v>
-      </c>
-      <c r="AC419">
-        <v>0.919</v>
-      </c>
-      <c r="AD419">
-        <v>1</v>
-      </c>
-      <c r="AE419">
-        <v>0.994</v>
-      </c>
-      <c r="AF419">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG419">
-        <v>1</v>
-      </c>
-      <c r="AH419" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI419" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ419" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="420" xml:space="preserve">
-      <c r="A420">
-        <v>46227</v>
-      </c>
-      <c r="B420" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C420" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D420" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E420">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F420">
-        <v>1</v>
-      </c>
-      <c r="G420">
-        <v>1</v>
-      </c>
-      <c r="H420">
-        <v>1</v>
-      </c>
-      <c r="I420">
-        <v>1</v>
-      </c>
-      <c r="J420">
-        <v>1</v>
-      </c>
-      <c r="K420">
-        <v>0.96</v>
-      </c>
-      <c r="M420">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N420">
-        <v>0.9912</v>
-      </c>
-      <c r="O420">
-        <v>1</v>
-      </c>
-      <c r="P420">
-        <v>1</v>
-      </c>
-      <c r="Q420">
-        <v>0.9583</v>
-      </c>
-      <c r="R420">
-        <v>0.9</v>
-      </c>
-      <c r="S420">
-        <v>0.9038</v>
-      </c>
-      <c r="U420" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V420">
-        <v>1</v>
-      </c>
-      <c r="W420">
-        <v>1</v>
-      </c>
-      <c r="X420">
-        <v>1</v>
-      </c>
-      <c r="Y420">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z420">
-        <v>0.946</v>
-      </c>
-      <c r="AA420">
-        <v>1</v>
-      </c>
-      <c r="AB420">
-        <v>1</v>
-      </c>
-      <c r="AC420">
-        <v>0.919</v>
-      </c>
-      <c r="AD420">
-        <v>1</v>
-      </c>
-      <c r="AE420">
-        <v>0.994</v>
-      </c>
-      <c r="AF420">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG420">
-        <v>1</v>
-      </c>
-      <c r="AH420" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI420" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ420" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="421" xml:space="preserve">
-      <c r="A421">
-        <v>46228</v>
-      </c>
-      <c r="B421" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C421" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D421" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E421">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F421">
-        <v>1</v>
-      </c>
-      <c r="G421">
-        <v>1</v>
-      </c>
-      <c r="H421">
-        <v>1</v>
-      </c>
-      <c r="I421">
-        <v>1</v>
-      </c>
-      <c r="J421">
-        <v>1</v>
-      </c>
-      <c r="K421">
-        <v>0.96</v>
-      </c>
-      <c r="M421">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N421">
-        <v>0.9912</v>
-      </c>
-      <c r="O421">
-        <v>1</v>
-      </c>
-      <c r="P421">
-        <v>1</v>
-      </c>
-      <c r="Q421">
-        <v>0.9583</v>
-      </c>
-      <c r="R421">
-        <v>0.9</v>
-      </c>
-      <c r="S421">
-        <v>0.9038</v>
-      </c>
-      <c r="U421" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V421">
-        <v>1</v>
-      </c>
-      <c r="W421">
-        <v>1</v>
-      </c>
-      <c r="X421">
-        <v>1</v>
-      </c>
-      <c r="Y421">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z421">
-        <v>0.946</v>
-      </c>
-      <c r="AA421">
-        <v>1</v>
-      </c>
-      <c r="AB421">
-        <v>1</v>
-      </c>
-      <c r="AC421">
-        <v>0.919</v>
-      </c>
-      <c r="AD421">
-        <v>1</v>
-      </c>
-      <c r="AE421">
-        <v>0.994</v>
-      </c>
-      <c r="AF421">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG421">
-        <v>1</v>
-      </c>
-      <c r="AH421" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI421" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ421" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="422" xml:space="preserve">
-      <c r="A422">
-        <v>46229</v>
-      </c>
-      <c r="B422" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C422" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D422" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E422">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F422">
-        <v>1</v>
-      </c>
-      <c r="G422">
-        <v>1</v>
-      </c>
-      <c r="H422">
-        <v>1</v>
-      </c>
-      <c r="I422">
-        <v>1</v>
-      </c>
-      <c r="J422">
-        <v>1</v>
-      </c>
-      <c r="K422">
-        <v>0.96</v>
-      </c>
-      <c r="M422">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N422">
-        <v>0.9912</v>
-      </c>
-      <c r="O422">
-        <v>1</v>
-      </c>
-      <c r="P422">
-        <v>1</v>
-      </c>
-      <c r="Q422">
-        <v>0.9583</v>
-      </c>
-      <c r="R422">
-        <v>0.9</v>
-      </c>
-      <c r="S422">
-        <v>0.9038</v>
-      </c>
-      <c r="U422" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V422">
-        <v>1</v>
-      </c>
-      <c r="W422">
-        <v>1</v>
-      </c>
-      <c r="X422">
-        <v>1</v>
-      </c>
-      <c r="Y422">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z422">
-        <v>0.946</v>
-      </c>
-      <c r="AA422">
-        <v>1</v>
-      </c>
-      <c r="AB422">
-        <v>1</v>
-      </c>
-      <c r="AC422">
-        <v>0.919</v>
-      </c>
-      <c r="AD422">
-        <v>1</v>
-      </c>
-      <c r="AE422">
-        <v>0.994</v>
-      </c>
-      <c r="AF422">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG422">
-        <v>1</v>
-      </c>
-      <c r="AH422" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI422" t="str">
-        <v>July</v>
-      </c>
-      <c r="AJ422" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="423" xml:space="preserve">
-      <c r="A423">
-        <v>46230</v>
-      </c>
-      <c r="B423" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C423" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D423" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E423">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F423">
-        <v>1</v>
-      </c>
-      <c r="G423">
-        <v>1</v>
-      </c>
-      <c r="H423">
-        <v>1</v>
-      </c>
-      <c r="I423">
-        <v>1</v>
-      </c>
-      <c r="J423">
-        <v>1</v>
-      </c>
-      <c r="K423">
-        <v>0.96</v>
-      </c>
-      <c r="M423">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N423">
-        <v>0.9912</v>
-      </c>
-      <c r="O423">
-        <v>1</v>
-      </c>
-      <c r="P423">
-        <v>1</v>
-      </c>
-      <c r="Q423">
-        <v>0.9583</v>
-      </c>
-      <c r="R423">
-        <v>0.9</v>
-      </c>
-      <c r="S423">
-        <v>0.9038</v>
-      </c>
-      <c r="U423" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V423">
-        <v>1</v>
-      </c>
-      <c r="W423">
-        <v>1</v>
-      </c>
-      <c r="X423">
-        <v>1</v>
-      </c>
-      <c r="Y423">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z423">
-        <v>0.946</v>
-      </c>
-      <c r="AA423">
-        <v>1</v>
-      </c>
-      <c r="AB423">
-        <v>1</v>
-      </c>
-      <c r="AC423">
-        <v>0.919</v>
-      </c>
-      <c r="AD423">
-        <v>1</v>
-      </c>
-      <c r="AE423">
-        <v>0.994</v>
-      </c>
-      <c r="AF423">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG423">
-        <v>1</v>
-      </c>
-      <c r="AH423" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-      <c r="AI423" t="str">
-        <v>Juli</v>
-      </c>
-      <c r="AJ423" t="str">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="424" xml:space="preserve">
-      <c r="A424">
-        <v>46231</v>
-      </c>
-      <c r="B424" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C424" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D424" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E424">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F424">
-        <v>1</v>
-      </c>
-      <c r="G424">
-        <v>1</v>
-      </c>
-      <c r="H424">
-        <v>1</v>
-      </c>
-      <c r="I424">
-        <v>1</v>
-      </c>
-      <c r="J424">
-        <v>1</v>
-      </c>
-      <c r="K424">
-        <v>0.96</v>
-      </c>
-      <c r="M424">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N424">
-        <v>0.9912</v>
-      </c>
-      <c r="O424">
-        <v>1</v>
-      </c>
-      <c r="P424">
-        <v>1</v>
-      </c>
-      <c r="Q424">
-        <v>0.9583</v>
-      </c>
-      <c r="R424">
-        <v>0.9</v>
-      </c>
-      <c r="S424">
-        <v>0.9038</v>
-      </c>
-      <c r="U424" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V424">
-        <v>1</v>
-      </c>
-      <c r="W424">
-        <v>1</v>
-      </c>
-      <c r="X424">
-        <v>1</v>
-      </c>
-      <c r="Y424">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z424">
-        <v>0.946</v>
-      </c>
-      <c r="AA424">
-        <v>1</v>
-      </c>
-      <c r="AB424">
-        <v>1</v>
-      </c>
-      <c r="AC424">
-        <v>0.919</v>
-      </c>
-      <c r="AD424">
-        <v>1</v>
-      </c>
-      <c r="AE424">
-        <v>0.994</v>
-      </c>
-      <c r="AF424">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG424">
-        <v>1</v>
-      </c>
-      <c r="AH424" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-    </row>
-    <row r="425" xml:space="preserve">
-      <c r="A425">
-        <v>46232</v>
-      </c>
-      <c r="B425" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C425" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D425" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E425">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F425">
-        <v>1</v>
-      </c>
-      <c r="G425">
-        <v>1</v>
-      </c>
-      <c r="H425">
-        <v>1</v>
-      </c>
-      <c r="I425">
-        <v>1</v>
-      </c>
-      <c r="J425">
-        <v>1</v>
-      </c>
-      <c r="K425">
-        <v>0.96</v>
-      </c>
-      <c r="M425">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N425">
-        <v>0.9912</v>
-      </c>
-      <c r="O425">
-        <v>1</v>
-      </c>
-      <c r="P425">
-        <v>1</v>
-      </c>
-      <c r="Q425">
-        <v>0.9583</v>
-      </c>
-      <c r="R425">
-        <v>0.9</v>
-      </c>
-      <c r="S425">
-        <v>0.9038</v>
-      </c>
-      <c r="U425" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V425">
-        <v>1</v>
-      </c>
-      <c r="W425">
-        <v>1</v>
-      </c>
-      <c r="X425">
-        <v>1</v>
-      </c>
-      <c r="Y425">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z425">
-        <v>0.946</v>
-      </c>
-      <c r="AA425">
-        <v>1</v>
-      </c>
-      <c r="AB425">
-        <v>1</v>
-      </c>
-      <c r="AC425">
-        <v>0.919</v>
-      </c>
-      <c r="AD425">
-        <v>1</v>
-      </c>
-      <c r="AE425">
-        <v>0.994</v>
-      </c>
-      <c r="AF425">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG425">
-        <v>1</v>
-      </c>
-      <c r="AH425" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-    </row>
-    <row r="426" xml:space="preserve">
-      <c r="A426">
-        <v>46233</v>
-      </c>
-      <c r="B426" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C426" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D426" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E426">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F426">
-        <v>1</v>
-      </c>
-      <c r="G426">
-        <v>1</v>
-      </c>
-      <c r="H426">
-        <v>1</v>
-      </c>
-      <c r="I426">
-        <v>1</v>
-      </c>
-      <c r="J426">
-        <v>1</v>
-      </c>
-      <c r="K426">
-        <v>0.96</v>
-      </c>
-      <c r="M426">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N426">
-        <v>0.9912</v>
-      </c>
-      <c r="O426">
-        <v>1</v>
-      </c>
-      <c r="P426">
-        <v>1</v>
-      </c>
-      <c r="Q426">
-        <v>0.9583</v>
-      </c>
-      <c r="R426">
-        <v>0.9</v>
-      </c>
-      <c r="S426">
-        <v>0.9038</v>
-      </c>
-      <c r="U426" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V426">
-        <v>1</v>
-      </c>
-      <c r="W426">
-        <v>1</v>
-      </c>
-      <c r="X426">
-        <v>1</v>
-      </c>
-      <c r="Y426">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z426">
-        <v>0.946</v>
-      </c>
-      <c r="AA426">
-        <v>1</v>
-      </c>
-      <c r="AB426">
-        <v>1</v>
-      </c>
-      <c r="AC426">
-        <v>0.919</v>
-      </c>
-      <c r="AD426">
-        <v>1</v>
-      </c>
-      <c r="AE426">
-        <v>0.994</v>
-      </c>
-      <c r="AF426">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG426">
-        <v>1</v>
-      </c>
-      <c r="AH426" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-    </row>
-    <row r="427" xml:space="preserve">
-      <c r="A427">
-        <v>46234</v>
-      </c>
-      <c r="B427" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C427" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D427" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E427">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F427">
-        <v>1</v>
-      </c>
-      <c r="G427">
-        <v>1</v>
-      </c>
-      <c r="H427">
-        <v>1</v>
-      </c>
-      <c r="I427">
-        <v>1</v>
-      </c>
-      <c r="J427">
-        <v>1</v>
-      </c>
-      <c r="K427">
-        <v>0.96</v>
-      </c>
-      <c r="M427">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N427">
-        <v>0.9912</v>
-      </c>
-      <c r="O427">
-        <v>1</v>
-      </c>
-      <c r="P427">
-        <v>1</v>
-      </c>
-      <c r="Q427">
-        <v>0.9583</v>
-      </c>
-      <c r="R427">
-        <v>0.9</v>
-      </c>
-      <c r="S427">
-        <v>0.9038</v>
-      </c>
-      <c r="U427" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V427">
-        <v>1</v>
-      </c>
-      <c r="W427">
-        <v>1</v>
-      </c>
-      <c r="X427">
-        <v>1</v>
-      </c>
-      <c r="Y427">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z427">
-        <v>0.946</v>
-      </c>
-      <c r="AA427">
-        <v>1</v>
-      </c>
-      <c r="AB427">
-        <v>1</v>
-      </c>
-      <c r="AC427">
-        <v>0.919</v>
-      </c>
-      <c r="AD427">
-        <v>1</v>
-      </c>
-      <c r="AE427">
-        <v>0.994</v>
-      </c>
-      <c r="AF427">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG427">
-        <v>1</v>
-      </c>
-      <c r="AH427" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-    </row>
-    <row r="428" xml:space="preserve">
-      <c r="A428">
-        <v>46235</v>
-      </c>
-      <c r="B428" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C428" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D428" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E428">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F428">
-        <v>1</v>
-      </c>
-      <c r="G428">
-        <v>1</v>
-      </c>
-      <c r="H428">
-        <v>1</v>
-      </c>
-      <c r="I428">
-        <v>1</v>
-      </c>
-      <c r="J428">
-        <v>1</v>
-      </c>
-      <c r="K428">
-        <v>0.96</v>
-      </c>
-      <c r="M428">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N428">
-        <v>0.9912</v>
-      </c>
-      <c r="O428">
-        <v>1</v>
-      </c>
-      <c r="P428">
-        <v>1</v>
-      </c>
-      <c r="Q428">
-        <v>0.9583</v>
-      </c>
-      <c r="R428">
-        <v>0.9</v>
-      </c>
-      <c r="S428">
-        <v>0.9038</v>
-      </c>
-      <c r="U428" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V428">
-        <v>1</v>
-      </c>
-      <c r="W428">
-        <v>1</v>
-      </c>
-      <c r="X428">
-        <v>1</v>
-      </c>
-      <c r="Y428">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z428">
-        <v>0.946</v>
-      </c>
-      <c r="AA428">
-        <v>1</v>
-      </c>
-      <c r="AB428">
-        <v>1</v>
-      </c>
-      <c r="AC428">
-        <v>0.919</v>
-      </c>
-      <c r="AD428">
-        <v>1</v>
-      </c>
-      <c r="AE428">
-        <v>0.994</v>
-      </c>
-      <c r="AF428">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG428">
-        <v>1</v>
-      </c>
-      <c r="AH428" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-    </row>
-    <row r="429" xml:space="preserve">
-      <c r="A429">
-        <v>46236</v>
-      </c>
-      <c r="B429" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C429" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D429" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E429">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F429">
-        <v>1</v>
-      </c>
-      <c r="G429">
-        <v>1</v>
-      </c>
-      <c r="H429">
-        <v>1</v>
-      </c>
-      <c r="I429">
-        <v>1</v>
-      </c>
-      <c r="J429">
-        <v>1</v>
-      </c>
-      <c r="K429">
-        <v>0.96</v>
-      </c>
-      <c r="M429">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N429">
-        <v>0.9912</v>
-      </c>
-      <c r="O429">
-        <v>1</v>
-      </c>
-      <c r="P429">
-        <v>1</v>
-      </c>
-      <c r="Q429">
-        <v>0.9583</v>
-      </c>
-      <c r="R429">
-        <v>0.9</v>
-      </c>
-      <c r="S429">
-        <v>0.9038</v>
-      </c>
-      <c r="U429" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V429">
-        <v>1</v>
-      </c>
-      <c r="W429">
-        <v>1</v>
-      </c>
-      <c r="X429">
-        <v>1</v>
-      </c>
-      <c r="Y429">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z429">
-        <v>0.946</v>
-      </c>
-      <c r="AA429">
-        <v>1</v>
-      </c>
-      <c r="AB429">
-        <v>1</v>
-      </c>
-      <c r="AC429">
-        <v>0.919</v>
-      </c>
-      <c r="AD429">
-        <v>1</v>
-      </c>
-      <c r="AE429">
-        <v>0.994</v>
-      </c>
-      <c r="AF429">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG429">
-        <v>1</v>
-      </c>
-      <c r="AH429" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-    </row>
-    <row r="430" xml:space="preserve">
-      <c r="A430">
-        <v>46237</v>
-      </c>
-      <c r="B430" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C430" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D430" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E430">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F430">
-        <v>1</v>
-      </c>
-      <c r="G430">
-        <v>1</v>
-      </c>
-      <c r="H430">
-        <v>1</v>
-      </c>
-      <c r="I430">
-        <v>1</v>
-      </c>
-      <c r="J430">
-        <v>1</v>
-      </c>
-      <c r="K430">
-        <v>0.96</v>
-      </c>
-      <c r="M430">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N430">
-        <v>0.9912</v>
-      </c>
-      <c r="O430">
-        <v>1</v>
-      </c>
-      <c r="P430">
-        <v>1</v>
-      </c>
-      <c r="Q430">
-        <v>0.9583</v>
-      </c>
-      <c r="R430">
-        <v>0.9</v>
-      </c>
-      <c r="S430">
-        <v>0.9038</v>
-      </c>
-      <c r="U430" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V430">
-        <v>1</v>
-      </c>
-      <c r="W430">
-        <v>1</v>
-      </c>
-      <c r="X430">
-        <v>1</v>
-      </c>
-      <c r="Y430">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z430">
-        <v>0.946</v>
-      </c>
-      <c r="AA430">
-        <v>1</v>
-      </c>
-      <c r="AB430">
-        <v>1</v>
-      </c>
-      <c r="AC430">
-        <v>0.919</v>
-      </c>
-      <c r="AD430">
-        <v>1</v>
-      </c>
-      <c r="AE430">
-        <v>0.994</v>
-      </c>
-      <c r="AF430">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG430">
-        <v>1</v>
-      </c>
-      <c r="AH430" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-    </row>
-    <row r="431" xml:space="preserve">
-      <c r="A431">
-        <v>46238</v>
-      </c>
-      <c r="B431" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C431" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D431" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E431">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F431">
-        <v>1</v>
-      </c>
-      <c r="G431">
-        <v>1</v>
-      </c>
-      <c r="H431">
-        <v>1</v>
-      </c>
-      <c r="I431">
-        <v>1</v>
-      </c>
-      <c r="J431">
-        <v>1</v>
-      </c>
-      <c r="K431">
-        <v>0.96</v>
-      </c>
-      <c r="M431">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N431">
-        <v>0.9912</v>
-      </c>
-      <c r="O431">
-        <v>1</v>
-      </c>
-      <c r="P431">
-        <v>1</v>
-      </c>
-      <c r="Q431">
-        <v>0.9583</v>
-      </c>
-      <c r="R431">
-        <v>0.9</v>
-      </c>
-      <c r="S431">
-        <v>0.9038</v>
-      </c>
-      <c r="U431" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V431">
-        <v>1</v>
-      </c>
-      <c r="W431">
-        <v>1</v>
-      </c>
-      <c r="X431">
-        <v>1</v>
-      </c>
-      <c r="Y431">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z431">
-        <v>0.946</v>
-      </c>
-      <c r="AA431">
-        <v>1</v>
-      </c>
-      <c r="AB431">
-        <v>1</v>
-      </c>
-      <c r="AC431">
-        <v>0.919</v>
-      </c>
-      <c r="AD431">
-        <v>1</v>
-      </c>
-      <c r="AE431">
-        <v>0.994</v>
-      </c>
-      <c r="AF431">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG431">
-        <v>1</v>
-      </c>
-      <c r="AH431" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-    </row>
-    <row r="432" xml:space="preserve">
-      <c r="A432">
-        <v>46239</v>
-      </c>
-      <c r="B432" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C432" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D432" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E432">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F432">
-        <v>1</v>
-      </c>
-      <c r="G432">
-        <v>1</v>
-      </c>
-      <c r="H432">
-        <v>1</v>
-      </c>
-      <c r="I432">
-        <v>1</v>
-      </c>
-      <c r="J432">
-        <v>1</v>
-      </c>
-      <c r="K432">
-        <v>0.96</v>
-      </c>
-      <c r="M432">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N432">
-        <v>0.9912</v>
-      </c>
-      <c r="O432">
-        <v>1</v>
-      </c>
-      <c r="P432">
-        <v>1</v>
-      </c>
-      <c r="Q432">
-        <v>0.9583</v>
-      </c>
-      <c r="R432">
-        <v>0.9</v>
-      </c>
-      <c r="S432">
-        <v>0.9038</v>
-      </c>
-      <c r="U432" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V432">
-        <v>1</v>
-      </c>
-      <c r="W432">
-        <v>1</v>
-      </c>
-      <c r="X432">
-        <v>1</v>
-      </c>
-      <c r="Y432">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z432">
-        <v>0.946</v>
-      </c>
-      <c r="AA432">
-        <v>1</v>
-      </c>
-      <c r="AB432">
-        <v>1</v>
-      </c>
-      <c r="AC432">
-        <v>0.919</v>
-      </c>
-      <c r="AD432">
-        <v>1</v>
-      </c>
-      <c r="AE432">
-        <v>0.994</v>
-      </c>
-      <c r="AF432">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG432">
-        <v>1</v>
-      </c>
-      <c r="AH432" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-    </row>
-    <row r="433" xml:space="preserve">
-      <c r="A433">
-        <v>46240</v>
-      </c>
-      <c r="B433" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C433" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D433" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E433">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F433">
-        <v>1</v>
-      </c>
-      <c r="G433">
-        <v>1</v>
-      </c>
-      <c r="H433">
-        <v>1</v>
-      </c>
-      <c r="I433">
-        <v>1</v>
-      </c>
-      <c r="J433">
-        <v>1</v>
-      </c>
-      <c r="K433">
-        <v>0.96</v>
-      </c>
-      <c r="M433">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N433">
-        <v>0.9912</v>
-      </c>
-      <c r="O433">
-        <v>1</v>
-      </c>
-      <c r="P433">
-        <v>1</v>
-      </c>
-      <c r="Q433">
-        <v>0.9583</v>
-      </c>
-      <c r="R433">
-        <v>0.9</v>
-      </c>
-      <c r="S433">
-        <v>0.9038</v>
-      </c>
-      <c r="U433" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-      <c r="V433">
-        <v>1</v>
-      </c>
-      <c r="W433">
-        <v>1</v>
-      </c>
-      <c r="X433">
-        <v>1</v>
-      </c>
-      <c r="Y433">
-        <v>0.800000000000001</v>
-      </c>
-      <c r="Z433">
-        <v>0.946</v>
-      </c>
-      <c r="AA433">
-        <v>1</v>
-      </c>
-      <c r="AB433">
-        <v>1</v>
-      </c>
-      <c r="AC433">
-        <v>0.919</v>
-      </c>
-      <c r="AD433">
-        <v>1</v>
-      </c>
-      <c r="AE433">
-        <v>0.994</v>
-      </c>
-      <c r="AF433">
-        <v>0.994000000000001</v>
-      </c>
-      <c r="AG433">
-        <v>1</v>
-      </c>
-      <c r="AH433" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Terdapat kerusakan kamera CCTV pada area landside. perimeter dan terminal.     _x000d_
-    Saat ini dilakukan proses perbaikan secara bertahap._x000d_
-2. Kerusakan 1 unit ETD pada part pump flow,polysulfone dan 5 micron .</v>
-      </c>
-    </row>
-    <row r="434" xml:space="preserve">
-      <c r="A434">
-        <v>46241</v>
-      </c>
-      <c r="B434" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C434" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D434" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E434">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F434">
-        <v>1</v>
-      </c>
-      <c r="G434">
-        <v>1</v>
-      </c>
-      <c r="H434">
-        <v>1</v>
-      </c>
-      <c r="I434">
-        <v>1</v>
-      </c>
-      <c r="J434">
-        <v>1</v>
-      </c>
-      <c r="K434">
-        <v>0.96</v>
-      </c>
-      <c r="M434">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N434">
-        <v>0.9912</v>
-      </c>
-      <c r="O434">
-        <v>1</v>
-      </c>
-      <c r="P434">
-        <v>1</v>
-      </c>
-      <c r="Q434">
-        <v>0.9583</v>
-      </c>
-      <c r="R434">
-        <v>0.9</v>
-      </c>
-      <c r="S434">
-        <v>0.9038</v>
-      </c>
-      <c r="U434" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-    </row>
-    <row r="435" xml:space="preserve">
-      <c r="A435">
-        <v>46242</v>
-      </c>
-      <c r="B435" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C435" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D435" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E435">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F435">
-        <v>1</v>
-      </c>
-      <c r="G435">
-        <v>1</v>
-      </c>
-      <c r="H435">
-        <v>1</v>
-      </c>
-      <c r="I435">
-        <v>1</v>
-      </c>
-      <c r="J435">
-        <v>1</v>
-      </c>
-      <c r="K435">
-        <v>0.96</v>
-      </c>
-      <c r="M435">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N435">
-        <v>0.9912</v>
-      </c>
-      <c r="O435">
-        <v>1</v>
-      </c>
-      <c r="P435">
-        <v>1</v>
-      </c>
-      <c r="Q435">
-        <v>0.9583</v>
-      </c>
-      <c r="R435">
-        <v>0.9</v>
-      </c>
-      <c r="S435">
-        <v>0.9038</v>
-      </c>
-      <c r="U435" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-    </row>
-    <row r="436" xml:space="preserve">
-      <c r="A436">
-        <v>46243</v>
-      </c>
-      <c r="B436" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C436" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D436" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E436">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F436">
-        <v>1</v>
-      </c>
-      <c r="G436">
-        <v>1</v>
-      </c>
-      <c r="H436">
-        <v>1</v>
-      </c>
-      <c r="I436">
-        <v>1</v>
-      </c>
-      <c r="J436">
-        <v>1</v>
-      </c>
-      <c r="K436">
-        <v>0.96</v>
-      </c>
-      <c r="M436">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N436">
-        <v>0.9912</v>
-      </c>
-      <c r="O436">
-        <v>1</v>
-      </c>
-      <c r="P436">
-        <v>1</v>
-      </c>
-      <c r="Q436">
-        <v>0.9583</v>
-      </c>
-      <c r="R436">
-        <v>0.9</v>
-      </c>
-      <c r="S436">
-        <v>0.9038</v>
-      </c>
-      <c r="U436" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-    </row>
-    <row r="437" xml:space="preserve">
-      <c r="A437">
-        <v>46244</v>
-      </c>
-      <c r="B437" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C437" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D437" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E437">
-        <v>0.899999999999999</v>
-      </c>
-      <c r="F437">
-        <v>1</v>
-      </c>
-      <c r="G437">
-        <v>1</v>
-      </c>
-      <c r="H437">
-        <v>1</v>
-      </c>
-      <c r="I437">
-        <v>1</v>
-      </c>
-      <c r="J437">
-        <v>1</v>
-      </c>
-      <c r="K437">
-        <v>0.96</v>
-      </c>
-      <c r="M437">
-        <f>13/14</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="N437">
-        <v>0.9912</v>
-      </c>
-      <c r="O437">
-        <v>1</v>
-      </c>
-      <c r="P437">
-        <v>1</v>
-      </c>
-      <c r="Q437">
-        <v>0.9583</v>
-      </c>
-      <c r="R437">
-        <v>0.9</v>
-      </c>
-      <c r="S437">
-        <v>0.9038</v>
-      </c>
-      <c r="U437" t="str" xml:space="preserve">
-        <v xml:space="preserve">- Chiller No. 1 T1B sensor oil temperatur error_x000d_
-- Kerusakan Salvage</v>
-      </c>
-    </row>
     <row r="496">
       <c r="F496">
         <f>AVERAGE(F285:K285)</f>
@@ -47856,107 +43244,6 @@
       </c>
       <c r="M522" t="str">
         <v>`</v>
-      </c>
-    </row>
-    <row r="1268">
-      <c r="A1268">
-        <v>46265</v>
-      </c>
-      <c r="B1268" t="str">
-        <v>Region 4</v>
-      </c>
-      <c r="C1268" t="str">
-        <v>Juanda Airport Surabaya</v>
-      </c>
-      <c r="D1268" t="str">
-        <v>SUB</v>
-      </c>
-      <c r="E1268">
-        <v>0.9</v>
-      </c>
-      <c r="F1268">
-        <v>1</v>
-      </c>
-      <c r="G1268">
-        <v>1</v>
-      </c>
-      <c r="H1268">
-        <v>1</v>
-      </c>
-      <c r="I1268">
-        <v>1</v>
-      </c>
-      <c r="J1268">
-        <v>1</v>
-      </c>
-      <c r="K1268">
-        <v>1</v>
-      </c>
-      <c r="L1268" t="str">
-        <v>1. Tegangan tidak stabil</v>
-      </c>
-      <c r="M1268">
-        <v>1</v>
-      </c>
-      <c r="N1268">
-        <v>1</v>
-      </c>
-      <c r="O1268">
-        <v>1</v>
-      </c>
-      <c r="P1268">
-        <v>1</v>
-      </c>
-      <c r="Q1268">
-        <v>1</v>
-      </c>
-      <c r="R1268">
-        <v>1</v>
-      </c>
-      <c r="S1268">
-        <v>1</v>
-      </c>
-      <c r="T1268">
-        <v>1</v>
-      </c>
-      <c r="V1268">
-        <v>1</v>
-      </c>
-      <c r="W1268">
-        <v>1</v>
-      </c>
-      <c r="X1268">
-        <v>1</v>
-      </c>
-      <c r="Y1268">
-        <v>1</v>
-      </c>
-      <c r="Z1268">
-        <v>1</v>
-      </c>
-      <c r="AA1268">
-        <v>1</v>
-      </c>
-      <c r="AB1268">
-        <v>1</v>
-      </c>
-      <c r="AC1268">
-        <v>1</v>
-      </c>
-      <c r="AD1268">
-        <v>1</v>
-      </c>
-      <c r="AE1268">
-        <v>1</v>
-      </c>
-      <c r="AF1268">
-        <v>1</v>
-      </c>
-      <c r="AG1268">
-        <v>1</v>
-      </c>
-      <c r="AH1268" t="str">
-        <v>1. Test log for WTMD device health checks</v>
       </c>
     </row>
   </sheetData>
